--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="481">
   <si>
     <t>Filename</t>
   </si>
@@ -808,652 +808,655 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9946,0.0004,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.0024,0.0000,0.9990</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.4773,0.0006,0.0000,0.7532</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9641,0.0051,0.0079,0.0023</t>
+  </si>
+  <si>
+    <t>0.0026,0.0961,0.0000,0.9871</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0350,0.0003,0.0000,0.9925</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9834,0.0005,0.0100,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0010,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.8713,0.0008,0.1668,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0000,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9983,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0000,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9246,0.0008,0.0765,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0104,0.0021,0.9882,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9990,0.0010</t>
+  </si>
+  <si>
+    <t>0.4735,0.5373,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9508,0.0641,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9998,0.0008</t>
+  </si>
+  <si>
+    <t>0.0143,0.9716,0.0107,0.0001</t>
+  </si>
+  <si>
+    <t>0.9889,0.0035,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9888,0.0020,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.1579,0.9002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9976,0.3067,0.0000</t>
+  </si>
+  <si>
+    <t>0.0819,0.4686,0.0580,0.0024</t>
+  </si>
+  <si>
+    <t>0.0040,0.0001,0.9955,0.0002</t>
+  </si>
+  <si>
+    <t>0.0259,0.0121,0.9539,0.0006</t>
+  </si>
+  <si>
+    <t>0.0039,0.0001,0.9899,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0129,0.2177,0.0770,0.7776</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9956,0.4288,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.0035,0.9935,0.0005</t>
+  </si>
+  <si>
+    <t>0.0142,0.0129,0.9799,0.0002</t>
+  </si>
+  <si>
+    <t>0.0285,0.0010,0.9777,0.0004</t>
+  </si>
+  <si>
+    <t>0.0042,0.0001,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0010,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.1099,0.0031,0.8547,0.0027</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0042,0.9992,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9991,0.0007,0.0000,0.0000</t>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9955,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0447,0.9917,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.0009,0.9952,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9948,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0103,0.9851,0.0036,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9561,0.0004,0.0383,0.0001</t>
+  </si>
+  <si>
+    <t>0.0805,0.0080,0.8988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0010,0.9983,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.9726,0.8451,0.0001</t>
+  </si>
+  <si>
+    <t>0.0109,0.7291,0.2989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9932,0.9755,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.0001,0.0059,0.9962</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.0003,0.9999</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9942,0.9508,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9893,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9877,0.0665,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9541,0.9887,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9965,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9745,0.9783,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0073,0.0048,0.9901,0.0002</t>
+  </si>
+  <si>
+    <t>0.9900,0.0001,0.0081,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.9947,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0262,0.9796,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.1436,0.0049,0.7983,0.0012</t>
+  </si>
+  <si>
+    <t>0.9395,0.0007,0.0477,0.0004</t>
+  </si>
+  <si>
+    <t>0.9811,0.0013,0.0056,0.0005</t>
+  </si>
+  <si>
+    <t>0.3784,0.0032,0.5534,0.0035</t>
+  </si>
+  <si>
+    <t>0.0010,0.1252,0.0052,0.9425</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9935,0.9783,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9980,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9324,0.0504,0.0072,0.0004</t>
+  </si>
+  <si>
+    <t>0.9870,0.0111,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9929,0.0037,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.4008,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.5332,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.3329,0.9772,0.0001</t>
+  </si>
+  <si>
+    <t>0.2579,0.0015,0.7866,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9748,0.0056,0.0071,0.0017</t>
+  </si>
+  <si>
+    <t>0.0264,0.0001,0.9867,0.0001</t>
+  </si>
+  <si>
+    <t>0.0363,0.0009,0.9742,0.0001</t>
+  </si>
+  <si>
+    <t>0.1004,0.0002,0.0012,0.9615</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0000,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9162,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0297,0.9728,0.0005,0.0030</t>
+  </si>
+  <si>
+    <t>0.6053,0.4329,0.0077,0.0023</t>
+  </si>
+  <si>
+    <t>0.7579,0.0001,0.0000,0.4108</t>
+  </si>
+  <si>
+    <t>0.0005,0.0067,0.9982,0.0065</t>
+  </si>
+  <si>
+    <t>0.9961,0.0000,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0326,0.9736,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6214,0.3261,0.0126,0.0007</t>
+  </si>
+  <si>
+    <t>0.9938,0.0032,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9465,0.0448,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9232,0.1028,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9479,0.0656,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0631,0.0333,0.9221,0.0002</t>
+  </si>
+  <si>
+    <t>0.9947,0.0058,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9887,0.0031,0.0037,0.0016</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9453,0.0534,0.0020,0.0021</t>
+  </si>
+  <si>
+    <t>0.0000,0.0105,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9669,0.0211,0.0051,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0439,0.9862,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.0006,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0055,0.0149,0.9870,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0029,0.0015,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0412,0.0003,0.9680,0.0003</t>
+  </si>
+  <si>
+    <t>0.2778,0.0037,0.7029,0.0007</t>
+  </si>
+  <si>
+    <t>0.1892,0.0028,0.8080,0.0001</t>
+  </si>
+  <si>
+    <t>0.0067,0.0223,0.9732,0.0003</t>
+  </si>
+  <si>
+    <t>0.6466,0.0158,0.2988,0.0005</t>
+  </si>
+  <si>
+    <t>0.9919,0.0002,0.0041,0.0002</t>
+  </si>
+  <si>
+    <t>0.2015,0.0003,0.8708,0.0001</t>
+  </si>
+  <si>
+    <t>0.3328,0.8065,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0329,0.9795,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4029,0.7534,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9967,0.0026,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0071,0.9940,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9025,0.0240,0.0038,0.0023</t>
+  </si>
+  <si>
+    <t>0.9924,0.0004,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.9235,0.0022,0.0614,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0005,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0124,0.0041,0.9682,0.0024</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0387,0.0010,0.9668,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0017,0.9942,0.0011</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0014,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0028,0.9975,0.0017</t>
+  </si>
+  <si>
+    <t>0.0957,0.0739,0.7812,0.0009</t>
+  </si>
+  <si>
+    <t>0.9666,0.0020,0.0090,0.0042</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0018,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.2744,0.9830,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0113,0.0002,0.9917,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0010,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.8089,0.0023,0.0830,0.0043</t>
+  </si>
+  <si>
+    <t>0.8630,0.0000,0.2727,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0001,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0004,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0029,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.7575,0.0014,0.3212,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.0009,0.9947,0.0004</t>
-  </si>
-  <si>
-    <t>0.0941,0.0011,0.9398,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.9942,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9653,0.0002,0.0425,0.0001</t>
-  </si>
-  <si>
-    <t>0.4306,0.0004,0.6960,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0006,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.1206,0.0001,0.9406,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.0006,0.9944,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.8184,0.1729,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.3056,0.4723,0.0516,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9951,0.0434,0.0000</t>
-  </si>
-  <si>
-    <t>0.9939,0.0019,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8594,0.1737,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9985,0.0167,0.0000</t>
-  </si>
-  <si>
-    <t>0.0842,0.4437,0.0412,0.0030</t>
-  </si>
-  <si>
-    <t>0.0003,0.0009,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0477,0.9943,0.0002</t>
-  </si>
-  <si>
-    <t>0.0032,0.0001,0.9939,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.4290,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9964,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9990,0.0005</t>
-  </si>
-  <si>
-    <t>0.0102,0.7806,0.0757,0.4197</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9983,0.0426,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0023,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0067,0.0017,0.9910,0.0003</t>
-  </si>
-  <si>
-    <t>0.0037,0.0019,0.9936,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0025,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0064,0.0046,0.9868,0.0007</t>
-  </si>
-  <si>
-    <t>0.9992,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9957,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0730,0.9882,0.0004</t>
-  </si>
-  <si>
-    <t>0.0032,0.0022,0.9928,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9959,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0080,0.9936,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9996,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0001,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.3152,0.0020,0.6981,0.0002</t>
-  </si>
-  <si>
-    <t>0.0037,0.0002,0.9975,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9862,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9114,0.9105,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0051,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9986,0.6245,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.0023,0.9989</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0015,0.9997</t>
-  </si>
-  <si>
-    <t>0.0024,0.0001,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.9631,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9717,0.8833,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.9120,0.1034,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.4640,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.6232,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9416,0.9617,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0102,0.0000,0.9937,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0013,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9986,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0356,0.9736,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.7632,0.0003,0.2735,0.0002</t>
-  </si>
-  <si>
-    <t>0.0604,0.0003,0.9511,0.0003</t>
-  </si>
-  <si>
-    <t>0.9496,0.0051,0.0177,0.0007</t>
-  </si>
-  <si>
-    <t>0.8409,0.0095,0.0439,0.0061</t>
-  </si>
-  <si>
-    <t>0.0002,0.3160,0.0095,0.8286</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9884,0.9860,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.2675,0.7734,0.0044,0.0001</t>
-  </si>
-  <si>
-    <t>0.4985,0.6276,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9584,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.4702,0.9942,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.1355,0.9786,0.0002</t>
-  </si>
-  <si>
-    <t>0.0054,0.0046,0.9902,0.0001</t>
-  </si>
-  <si>
-    <t>0.9861,0.0013,0.0044,0.0003</t>
-  </si>
-  <si>
-    <t>0.5924,0.0000,0.6031,0.0000</t>
-  </si>
-  <si>
-    <t>0.5564,0.0068,0.4137,0.0005</t>
-  </si>
-  <si>
-    <t>0.1351,0.0001,0.0013,0.9471</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0248,0.0002,0.0000,0.9926</t>
-  </si>
-  <si>
-    <t>0.0000,0.9905,0.8448,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0009,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.9943,0.0010,0.0195</t>
-  </si>
-  <si>
-    <t>0.5283,0.5301,0.0023,0.0012</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.4508,0.0000,0.0005,0.6208</t>
-  </si>
-  <si>
-    <t>0.0004,0.0019,0.9983,0.0081</t>
-  </si>
-  <si>
-    <t>0.9425,0.0004,0.0250,0.0081</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0163,0.9836,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8359,0.1695,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9840,0.0075,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9643,0.0259,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9930,0.0065,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0773,0.9484,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0219,0.1631,0.9317,0.0001</t>
-  </si>
-  <si>
-    <t>0.9935,0.0081,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9938,0.0022,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9525,0.0468,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0068,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9953,0.0022,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0081,0.0359,0.9564,0.0044</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0064,0.0202,0.9766,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0110,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.9979,0.0003</t>
-  </si>
-  <si>
-    <t>0.0083,0.0011,0.9892,0.0004</t>
-  </si>
-  <si>
-    <t>0.2457,0.0063,0.7281,0.0006</t>
-  </si>
-  <si>
-    <t>0.1159,0.0012,0.9221,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0049,0.9952,0.0001</t>
-  </si>
-  <si>
-    <t>0.9747,0.0023,0.0120,0.0002</t>
-  </si>
-  <si>
-    <t>0.9724,0.0004,0.0158,0.0009</t>
-  </si>
-  <si>
-    <t>0.9400,0.0128,0.0200,0.0004</t>
-  </si>
-  <si>
-    <t>0.7344,0.4532,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.9980,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.7583,0.3927,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9164,0.0930,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.1688,0.8892,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9438,0.0194,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9451,0.0008,0.0280,0.0018</t>
-  </si>
-  <si>
-    <t>0.9624,0.0037,0.0185,0.0004</t>
-  </si>
-  <si>
-    <t>0.1432,0.0049,0.8759,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0661,0.0064,0.8723,0.0018</t>
-  </si>
-  <si>
-    <t>0.0002,0.0014,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0063,0.0009,0.9912,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0064,0.9887,0.0011</t>
-  </si>
-  <si>
-    <t>0.9977,0.0014,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0058,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0015,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0015,0.9990,0.0005</t>
-  </si>
-  <si>
-    <t>0.0760,0.3232,0.5190,0.0011</t>
-  </si>
-  <si>
-    <t>0.9890,0.0004,0.0038,0.0008</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.5316,0.9674,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0098,0.0009,0.9895,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0054,0.0015,0.9931,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0046,0.9968,0.0003</t>
-  </si>
-  <si>
-    <t>0.9805,0.0009,0.0078,0.0003</t>
-  </si>
-  <si>
-    <t>0.9869,0.0000,0.0205,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9924,0.0101,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0022,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0130,0.0027,0.9835,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0178,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0017,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.0045,0.9918,0.0021</t>
-  </si>
-  <si>
-    <t>0.0037,0.0003,0.9944,0.0017</t>
-  </si>
-  <si>
-    <t>0.2612,0.0005,0.7951,0.0009</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.9981,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0017,0.0183,0.0000,0.9970</t>
-  </si>
-  <si>
-    <t>0.0316,0.0001,0.0001,0.9928</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9805,0.0011,0.0058,0.0019</t>
+    <t>0.9979,0.0015,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0072,0.0009,0.9924,0.0015</t>
+  </si>
+  <si>
+    <t>0.0004,0.0189,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0052,0.0083,0.9824,0.0012</t>
+  </si>
+  <si>
+    <t>0.0008,0.0005,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0101,0.0010,0.9880,0.0041</t>
+  </si>
+  <si>
+    <t>0.0377,0.0023,0.9670,0.0010</t>
+  </si>
+  <si>
+    <t>0.0038,0.0001,0.9948,0.0006</t>
+  </si>
+  <si>
+    <t>0.9911,0.0004,0.0000,0.0058</t>
+  </si>
+  <si>
+    <t>0.0011,0.0226,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.0143,0.0001,0.0003,0.9965</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0002,0.0001</t>
   </si>
 </sst>
 </file>
@@ -1839,7 +1842,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1853,7 +1856,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1867,7 +1870,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1881,7 +1884,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1895,7 +1898,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1909,7 +1912,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1923,7 +1926,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1937,7 +1940,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1951,7 +1954,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1965,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1979,7 +1982,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1993,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2007,7 +2010,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2021,7 +2024,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2032,10 +2035,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2049,7 +2052,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2063,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2077,7 +2080,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2119,7 +2122,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2133,7 +2136,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2147,7 +2150,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2158,10 +2161,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2175,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2189,7 +2192,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2203,7 +2206,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2217,7 +2220,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2231,7 +2234,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2242,10 +2245,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2259,7 +2262,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2273,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2287,7 +2290,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2301,7 +2304,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2315,7 +2318,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2326,10 +2329,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2343,7 +2346,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2354,10 +2357,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2371,7 +2374,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2385,7 +2388,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2399,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2413,7 +2416,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2427,7 +2430,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2441,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2452,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2469,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2483,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2497,7 +2500,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2511,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2525,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2539,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2553,7 +2556,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2567,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2581,7 +2584,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2595,7 +2598,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2609,7 +2612,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2623,7 +2626,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2637,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2651,7 +2654,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2665,7 +2668,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2679,7 +2682,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2693,7 +2696,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2707,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2721,7 +2724,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2735,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2749,7 +2752,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2763,7 +2766,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2777,7 +2780,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2791,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2805,7 +2808,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2819,7 +2822,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2833,7 +2836,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2844,10 +2847,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2861,7 +2864,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2875,7 +2878,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2889,7 +2892,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2903,7 +2906,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2917,7 +2920,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2931,7 +2934,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2945,7 +2948,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2959,7 +2962,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2973,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2987,7 +2990,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3001,7 +3004,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3012,10 +3015,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3029,7 +3032,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3043,7 +3046,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3057,7 +3060,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3071,7 +3074,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3085,7 +3088,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3099,7 +3102,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3113,7 +3116,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3127,7 +3130,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3141,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3155,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3169,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3183,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3197,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3211,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3225,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>348</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3239,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3253,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>351</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3267,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3281,7 +3284,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3295,7 +3298,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3309,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3323,7 +3326,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3337,7 +3340,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3351,7 +3354,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3393,7 +3396,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3407,7 +3410,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>282</v>
+        <v>360</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3421,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3432,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3446,10 +3449,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3463,7 +3466,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3474,10 +3477,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3491,7 +3494,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3505,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3519,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>283</v>
+        <v>368</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3533,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3547,7 +3550,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3561,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3572,10 +3575,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3586,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3603,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3617,7 +3620,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3631,7 +3634,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3645,7 +3648,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3659,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3673,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3687,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>321</v>
+        <v>376</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3701,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3712,10 +3715,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3726,10 +3729,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3743,7 +3746,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3757,7 +3760,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3771,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>268</v>
+        <v>382</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3785,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3799,7 +3802,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3810,10 +3813,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3827,7 +3830,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3841,7 +3844,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3855,7 +3858,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3869,7 +3872,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3883,7 +3886,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3897,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3911,7 +3914,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3925,7 +3928,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3936,10 +3939,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3953,7 +3956,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>389</v>
+        <v>351</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3964,10 +3967,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3981,7 +3984,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3995,7 +3998,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4009,7 +4012,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4023,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4037,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4051,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4065,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4079,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4093,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4107,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4121,7 +4124,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>268</v>
+        <v>402</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4135,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4149,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4163,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4177,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4191,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>401</v>
+        <v>271</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4205,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4219,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4233,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4247,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4258,10 +4261,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4275,7 +4278,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4289,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4303,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4317,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4331,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4345,7 +4348,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4359,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4373,7 +4376,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4387,7 +4390,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4401,7 +4404,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4415,7 +4418,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4429,7 +4432,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4443,7 +4446,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4457,7 +4460,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4471,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4485,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4499,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4513,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4527,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4541,7 +4544,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4555,7 +4558,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4566,10 +4569,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4580,10 +4583,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4597,7 +4600,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4608,10 +4611,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4625,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4639,7 +4642,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4653,7 +4656,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4667,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4681,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4695,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4706,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4723,7 +4726,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4737,7 +4740,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4751,7 +4754,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4765,7 +4768,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4779,7 +4782,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4793,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4807,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4821,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4835,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>445</v>
+        <v>314</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4849,7 +4852,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4863,7 +4866,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4877,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4891,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4905,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4919,7 +4922,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4933,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4947,7 +4950,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4961,7 +4964,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4972,10 +4975,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4989,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5003,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5017,7 +5020,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5031,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5045,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5059,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5073,7 +5076,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5087,7 +5090,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5101,7 +5104,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5115,7 +5118,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5129,7 +5132,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5143,7 +5146,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5157,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5171,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>466</v>
+        <v>320</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5185,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5199,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5213,7 +5216,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5227,7 +5230,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5241,7 +5244,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5255,7 +5258,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5269,7 +5272,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5283,7 +5286,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5297,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5311,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5325,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5339,7 +5342,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5353,7 +5356,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5367,7 +5370,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>478</v>
+        <v>337</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5381,7 +5384,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5395,7 +5398,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
